--- a/data/trans_dic/IQ2606_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ2606_R2-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52,31%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79,99%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>61,05%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>84,89%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,15; 69,8</t>
+          <t>43,88; 61,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,84; 91,02</t>
+          <t>76,67; 89,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,87; 92,65</t>
+          <t>68,32; 90,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,51; 61,2</t>
+          <t>52,45; 69,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,1; 89,16</t>
+          <t>77,22; 90,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,85; 88,29</t>
+          <t>70,15; 92,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,46; 63,33</t>
+          <t>51,05; 62,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79,33; 88,41</t>
+          <t>80,05; 88,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,46; 88,12</t>
+          <t>71,81; 88,63</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>69,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>68,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>77,94%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,03; 76,8</t>
+          <t>61,81; 76,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,66; 84,48</t>
+          <t>69,87; 82,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,72; 91,83</t>
+          <t>75,34; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,6; 76,73</t>
+          <t>60,46; 76,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,56; 81,97</t>
+          <t>70,39; 84,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,62; 100,0</t>
+          <t>68,45; 92,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,24; 74,36</t>
+          <t>63,49; 74,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,51; 81,35</t>
+          <t>72,28; 81,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78,84; 94,05</t>
+          <t>77,33; 93,46</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62,11%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>62,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>63,8%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74,11%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62,11%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,01%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,2; 70,97</t>
+          <t>53,17; 70,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,71; 72,55</t>
+          <t>64,85; 80,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,44; 91,12</t>
+          <t>74,57; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,08; 70,28</t>
+          <t>54,73; 71,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,0; 81,42</t>
+          <t>53,45; 73,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,02; 100,0</t>
+          <t>46,9; 90,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,1; 68,1</t>
+          <t>56,33; 68,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,91; 74,87</t>
+          <t>61,5; 74,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,39; 93,52</t>
+          <t>68,54; 92,8</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54,96%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>62,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>72,64%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54,96%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,66; 67,7</t>
+          <t>48,92; 60,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,36; 77,51</t>
+          <t>65,05; 75,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,58; 95,12</t>
+          <t>84,49; 98,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,37; 60,59</t>
+          <t>57,05; 68,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,84; 75,59</t>
+          <t>67,43; 77,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,27; 97,58</t>
+          <t>75,08; 94,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,43; 62,23</t>
+          <t>54,95; 62,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,14; 75,11</t>
+          <t>67,7; 75,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,83; 95,27</t>
+          <t>84,5; 95,38</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69,23%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>56,77%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>64,8%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>87,76%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>52,25%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,31; 63,81</t>
+          <t>45,53; 60,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,68; 70,73</t>
+          <t>62,31; 75,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,59; 95,23</t>
+          <t>67,51; 89,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,37; 60,02</t>
+          <t>49,97; 63,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,79; 75,89</t>
+          <t>57,65; 71,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,16; 89,16</t>
+          <t>70,01; 94,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,31; 59,73</t>
+          <t>49,91; 59,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,02; 71,5</t>
+          <t>62,48; 71,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,94; 90,19</t>
+          <t>70,85; 88,03</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68,84%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>86,71%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>59,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>74,53%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76,74%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,35; 70,84</t>
+          <t>43,59; 63,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,21; 82,57</t>
+          <t>59,57; 77,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,8; 92,45</t>
+          <t>69,03; 95,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,05; 63,68</t>
+          <t>47,98; 71,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,68; 76,98</t>
+          <t>63,31; 83,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,18; 96,81</t>
+          <t>45,19; 93,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,44; 63,39</t>
+          <t>49,28; 63,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,31; 78,13</t>
+          <t>64,42; 78,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71,6; 92,89</t>
+          <t>67,31; 92,5</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>56,83%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73,07%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>61,8%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>72,69%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>83,82%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>73,07%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,01%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,67; 64,86</t>
+          <t>53,64; 59,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,33; 75,19</t>
+          <t>70,16; 75,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,96; 88,77</t>
+          <t>81,51; 90,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53,56; 60,09</t>
+          <t>58,52; 64,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,09; 75,58</t>
+          <t>69,76; 75,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,33; 90,85</t>
+          <t>77,0; 87,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,18; 61,5</t>
+          <t>57,07; 61,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,9; 74,79</t>
+          <t>70,83; 74,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>81,97; 88,62</t>
+          <t>80,91; 88,14</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44555</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81507</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29425</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>52900</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>67892</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25182</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44555</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81507</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54765</t>
+          <t>54511</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45188; 60476</t>
+          <t>37371; 52138</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62248; 72788</t>
+          <t>74496; 86944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20712; 27865</t>
+          <t>25131; 33200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37057; 52126</t>
+          <t>45445; 59913</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74913; 86636</t>
+          <t>61757; 72106</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24053; 33260</t>
+          <t>21131; 27961</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86707; 108806</t>
+          <t>87706; 107942</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>140519; 156611</t>
+          <t>141800; 157088</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48411; 59702</t>
+          <t>48046; 59299</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>64848</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84732</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18635</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>62798</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>80466</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20035</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64848</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84732</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>39207</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54821; 70126</t>
+          <t>57698; 71498</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72945; 87214</t>
+          <t>77840; 91947</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16007; 22366</t>
+          <t>14999; 19910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57500; 71627</t>
+          <t>55206; 69774</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76376; 91323</t>
+          <t>72669; 86874</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16705; 21248</t>
+          <t>17025; 23072</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>116775; 137324</t>
+          <t>117244; 137371</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>153493; 174621</t>
+          <t>155150; 175515</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35955; 42891</t>
+          <t>34629; 41852</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51454</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54097</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14956</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>52526</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>39456</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8566</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51454</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>54097</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>23613</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44370; 59190</t>
+          <t>44048; 58743</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33212; 44866</t>
+          <t>48049; 59824</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4790; 10532</t>
+          <t>12105; 16233</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43973; 58223</t>
+          <t>45642; 59876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46682; 60329</t>
+          <t>33052; 45288</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13608; 17668</t>
+          <t>5557; 10675</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93264; 113210</t>
+          <t>93651; 113877</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84157; 101772</t>
+          <t>83606; 100887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19987; 27333</t>
+          <t>19246; 26058</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>120416</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147193</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39724</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>124807</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>159872</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>120416</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>147193</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43586</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76586</t>
+          <t>70881</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>112909; 134904</t>
+          <t>107176; 132256</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148262; 170592</t>
+          <t>135929; 158258</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28747; 35704</t>
+          <t>35795; 41523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108153; 132743</t>
+          <t>113678; 135565</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>135489; 157950</t>
+          <t>148415; 170247</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39363; 45584</t>
+          <t>26765; 33692</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>227702; 260331</t>
+          <t>229893; 262380</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>292370; 322285</t>
+          <t>290496; 322585</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71466; 80262</t>
+          <t>65927; 74412</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>72459</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98380</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>31457</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>81886</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>87494</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20347</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>72459</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98380</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33709</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>54056</t>
+          <t>48395</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>71123; 92031</t>
+          <t>63138; 83476</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77878; 95509</t>
+          <t>88548; 107027</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17293; 22080</t>
+          <t>26664; 35244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62914; 83242</t>
+          <t>72075; 91726</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>89229; 107839</t>
+          <t>77849; 96303</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28143; 37359</t>
+          <t>13961; 18837</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139514; 168971</t>
+          <t>141212; 168555</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>171881; 198137</t>
+          <t>173157; 198716</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>48125; 58703</t>
+          <t>42109; 52322</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>38318</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46689</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>18050</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>31015</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>45081</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9990</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>38318</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>46689</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>28367</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24626; 36842</t>
+          <t>30837; 44702</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38840; 49948</t>
+          <t>40403; 52716</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6222; 12035</t>
+          <t>14369; 19895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31873; 45048</t>
+          <t>24954; 36937</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39798; 52208</t>
+          <t>38294; 50276</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16289; 22794</t>
+          <t>6172; 12795</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59463; 77817</t>
+          <t>60497; 78216</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82517; 100248</t>
+          <t>82666; 100601</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26181; 33964</t>
+          <t>23204; 31888</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>592</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>729</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>183</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>392050</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>512597</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>152247</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>405932</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>480262</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>117121</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>392050</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>512597</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>163781</t>
+          <t>112727</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>280902</t>
+          <t>264973</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>385387; 426032</t>
+          <t>370024; 412673</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>458042; 496747</t>
+          <t>492215; 530431</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108928; 124039</t>
+          <t>143135; 158809</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>369518; 414526</t>
+          <t>384375; 425291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>491719; 530240</t>
+          <t>460880; 500048</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>155402; 171480</t>
+          <t>104790; 119475</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>770095; 828197</t>
+          <t>768513; 828175</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>965794; 1018869</t>
+          <t>964827; 1019000</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>269262; 291090</t>
+          <t>252200; 274743</t>
         </is>
       </c>
     </row>
